--- a/MORE_HD_master_confirmatory_240runs.xlsx
+++ b/MORE_HD_master_confirmatory_240runs.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_JalurB_Selection" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Schema_Map'!$A$3:$G$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Schema_Map'!$A$3:$G$328</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'15_Classical_Baselines'!$A$3:$V$363</definedName>
   </definedNames>
 </workbook>
@@ -26021,7 +26021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G326"/>
+  <dimension ref="A1:G328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29398,74 +29398,74 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>03_Clustering_History</t>
+          <t>02_Run_Config</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>val_monitor_policy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>per_eval</t>
+          <t>per_run</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>val_monitor_policy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>Dikunci 2026-10-01 (G3-05b): FULL_VAL (prefilled); STRATIFIED_FIXED_SUBSET hanya bila pilot timing membuktikan tidak layak, berlaku global</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>03_Clustering_History</t>
+          <t>02_Run_Config</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>n_val_monitor_per_class</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>per_eval</t>
+          <t>per_run</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>n_val_monitor_per_class</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>G3-05b: kosong (NULL) pada FULL_VAL; angka tunggal dikunci sebelum pilot konvergensi bila fallback aktif</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -29487,17 +29487,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -29509,7 +29514,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -29519,17 +29524,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -29541,7 +29551,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -29556,7 +29566,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -29573,7 +29583,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -29588,7 +29598,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -29605,7 +29615,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>eval_id</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -29615,22 +29625,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>logs/clustering_log.jsonl</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>eval_id</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>0-based</t>
         </is>
       </c>
     </row>
@@ -29642,7 +29647,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -29652,22 +29657,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>logs/clustering_log.jsonl</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>G1-06</t>
         </is>
       </c>
     </row>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>train_loss</t>
+          <t>eval_id</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>train_loss</t>
+          <t>eval_id</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -29704,7 +29704,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Objective COBYLA</t>
+          <t>0-based</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>pseudo_accuracy_val</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -29731,7 +29731,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>pseudo_accuracy_val</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Selector Jalur B kriteria 1; centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
+          <t>G1-06</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>avg_margin_val</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>avg_margin_val</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Diagnostik</t>
+          <t>Objective COBYLA</t>
         </is>
       </c>
     </row>
@@ -29790,7 +29790,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>mean_true_distance_val</t>
+          <t>pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>mean_true_distance_val</t>
+          <t>pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Selector Jalur B kriteria 3</t>
+          <t>Selector Jalur B kriteria 1; centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>min_separation_val</t>
+          <t>avg_margin_val</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -29842,7 +29842,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>min_separation_val</t>
+          <t>avg_margin_val</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -29852,7 +29852,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Selector Jalur B kriteria 2</t>
+          <t>Diagnostik</t>
         </is>
       </c>
     </row>
@@ -29864,7 +29864,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>mean_true_distance_val</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -29879,7 +29879,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>mean_true_distance_val</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -29889,7 +29889,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
+          <t>Selector Jalur B kriteria 3</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>min_separation_ratio</t>
+          <t>min_separation_val</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>min_separation_ratio</t>
+          <t>min_separation_val</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>min_separation / (1 + 1/(K-1)); centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
+          <t>Selector Jalur B kriteria 2</t>
         </is>
       </c>
     </row>
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>closest_class_i</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>closest_class_i</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -29963,7 +29963,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pasangan penentu min_separation</t>
+          <t>centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
         </is>
       </c>
     </row>
@@ -29975,7 +29975,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>closest_class_j</t>
+          <t>min_separation_ratio</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>closest_class_j</t>
+          <t>min_separation_ratio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -30000,7 +30000,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pasangan penentu min_separation</t>
+          <t>min_separation / (1 + 1/(K-1)); centroid rumus MORE dari 5 sampel clustering/kelas (G2-07)</t>
         </is>
       </c>
     </row>
@@ -30012,7 +30012,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>correlation_consistency</t>
+          <t>closest_class_i</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -30027,12 +30027,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>correlation_consistency</t>
+          <t>closest_class_i</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Pasangan penentu min_separation</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30049,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>active_dimensions</t>
+          <t>closest_class_j</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -30059,12 +30064,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>active_dimensions</t>
+          <t>closest_class_j</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Pasangan penentu min_separation</t>
         </is>
       </c>
     </row>
@@ -30076,7 +30086,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>yodd_norm_fraction</t>
+          <t>correlation_consistency</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -30086,22 +30096,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logs/clustering_log.jsonl</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>correlation_consistency</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Definisi menunggu G2-05</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30118,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>eval_runtime_sec</t>
+          <t>active_dimensions</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -30128,17 +30133,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>eval_runtime_sec</t>
+          <t>active_dimensions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Dibutuhkan pilot §1.1</t>
         </is>
       </c>
     </row>
@@ -30150,7 +30150,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>n_degenerate_cluster_outputs</t>
+          <t>yodd_norm_fraction</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -30160,22 +30160,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>logs/clustering_log.jsonl</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>n_degenerate_cluster_outputs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>G2-04; output 5 sampel clustering/kelas dengan norm &lt; eps_norm (fallback 1.0 di pair loss); normal = 0</t>
+          <t>Definisi menunggu G2-05</t>
         </is>
       </c>
     </row>
@@ -30187,7 +30187,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>n_degenerate_val_outputs</t>
+          <t>eval_runtime_sec</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>n_degenerate_val_outputs</t>
+          <t>eval_runtime_sec</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>G2-04; output validation dengan norm &lt; eps_norm</t>
+          <t>Dibutuhkan pilot §1.1</t>
         </is>
       </c>
     </row>
@@ -30224,7 +30224,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>n_degenerate_centroids_train</t>
+          <t>n_degenerate_cluster_outputs</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -30239,7 +30239,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>n_degenerate_centroids_train</t>
+          <t>n_degenerate_cluster_outputs</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>G2-04; &gt;0 -&gt; eval_id tidak eligible untuk Jalur B</t>
+          <t>G2-04; output 5 sampel clustering/kelas dengan norm &lt; eps_norm (fallback 1.0 di pair loss); normal = 0</t>
         </is>
       </c>
     </row>
@@ -30261,7 +30261,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>n_degenerate_centroids_val</t>
+          <t>n_degenerate_val_outputs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>n_degenerate_centroids_val</t>
+          <t>n_degenerate_val_outputs</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>G2-04; &gt;0 -&gt; eval_id tidak eligible untuk Jalur B</t>
+          <t>G2-04; output validation dengan norm &lt; eps_norm</t>
         </is>
       </c>
     </row>
@@ -30298,7 +30298,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>min_centroid_prenorm_train</t>
+          <t>n_degenerate_centroids_train</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>min_centroid_prenorm_train</t>
+          <t>n_degenerate_centroids_train</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -30323,19 +30323,19 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>G2-04/G2-07; norm terkecil median unit-vector sebelum normalisasi</t>
+          <t>G2-04; &gt;0 -&gt; eval_id tidak eligible untuk Jalur B</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>04_Supervised_History</t>
+          <t>03_Clustering_History</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>n_degenerate_centroids_val</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -30345,34 +30345,34 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/clustering_log.jsonl</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>n_degenerate_centroids_val</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>G2-04; &gt;0 -&gt; eval_id tidak eligible untuk Jalur B</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>04_Supervised_History</t>
+          <t>03_Clustering_History</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>min_centroid_prenorm_train</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -30382,22 +30382,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/clustering_log.jsonl</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>min_centroid_prenorm_train</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>G2-04/G2-07; norm terkecil median unit-vector sebelum normalisasi</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -30419,17 +30419,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -30441,7 +30446,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -30451,17 +30456,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30483,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -30488,7 +30498,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -30505,7 +30515,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -30520,7 +30530,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -30537,7 +30547,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>eval_id</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -30547,22 +30557,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>logs/supervised_log.jsonl</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>eval_id</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>0-based</t>
         </is>
       </c>
     </row>
@@ -30574,7 +30579,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -30584,22 +30589,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>logs/supervised_log.jsonl</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>G1-06</t>
         </is>
       </c>
     </row>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>train_loss</t>
+          <t>eval_id</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>train_loss</t>
+          <t>eval_id</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Objective COBYLA</t>
+          <t>0-based</t>
         </is>
       </c>
     </row>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>val_loss</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -30663,7 +30663,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>val_loss</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -30673,7 +30673,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pasif</t>
+          <t>G1-06</t>
         </is>
       </c>
     </row>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>pseudo_accuracy_val</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>pseudo_accuracy_val</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -30710,7 +30710,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pasif; quantum label terdekat</t>
+          <t>Objective COBYLA</t>
         </is>
       </c>
     </row>
@@ -30722,7 +30722,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>avg_margin_val</t>
+          <t>val_loss</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>avg_margin_val</t>
+          <t>val_loss</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>eval_runtime_sec</t>
+          <t>pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -30774,12 +30774,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>eval_runtime_sec</t>
+          <t>pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Pasif; quantum label terdekat</t>
         </is>
       </c>
     </row>
@@ -30791,7 +30796,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>n_degenerate_train_outputs</t>
+          <t>avg_margin_val</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -30806,7 +30811,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>n_degenerate_train_outputs</t>
+          <t>avg_margin_val</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30816,7 +30821,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>G2-04; diagnostik</t>
+          <t>Pasif</t>
         </is>
       </c>
     </row>
@@ -30828,7 +30833,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>n_degenerate_val_outputs</t>
+          <t>eval_runtime_sec</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -30843,91 +30848,86 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>n_degenerate_val_outputs</t>
+          <t>eval_runtime_sec</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>G2-04; diagnostik</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>05_Correlation_Matrix</t>
+          <t>04_Supervised_History</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>n_degenerate_train_outputs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>per_class_pair</t>
+          <t>per_eval</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/supervised_log.jsonl</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>n_degenerate_train_outputs</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>G2-04; diagnostik</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>05_Correlation_Matrix</t>
+          <t>04_Supervised_History</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>n_degenerate_val_outputs</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>per_class_pair</t>
+          <t>per_eval</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/supervised_log.jsonl</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>n_degenerate_val_outputs</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>G2-04; diagnostik</t>
         </is>
       </c>
     </row>
@@ -30939,7 +30939,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -30949,17 +30949,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -30971,7 +30976,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -30981,17 +30986,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -31003,7 +31013,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -31018,7 +31028,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -31035,7 +31045,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -31050,7 +31060,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -31067,7 +31077,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>class_i</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -31082,17 +31092,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Pasangan terurut kelas</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -31104,7 +31109,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>class_j</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -31119,12 +31124,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31141,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>raw_mse</t>
+          <t>class_i</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -31146,22 +31151,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pseudocode hanya menyimpan S (correlation_matrix.npy); raw MSE belum disimpan (G3-02/G4-04)</t>
+          <t>Pasangan terurut kelas</t>
         </is>
       </c>
     </row>
@@ -31173,7 +31178,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S_value</t>
+          <t>class_j</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -31183,91 +31188,86 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>artifacts/correlation_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>S[i][j]</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06_Quantum_Labels</t>
+          <t>05_Correlation_Matrix</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>raw_mse</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>per_class</t>
+          <t>per_class_pair</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>Pseudocode hanya menyimpan S (correlation_matrix.npy); raw MSE belum disimpan (G3-02/G4-04)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06_Quantum_Labels</t>
+          <t>05_Correlation_Matrix</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>S_value</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>per_class</t>
+          <t>per_class_pair</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/correlation_matrix.npy</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>S[i][j]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -31279,7 +31279,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -31289,17 +31289,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -31311,7 +31316,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -31321,17 +31326,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31353,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -31358,7 +31368,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -31375,7 +31385,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -31390,7 +31400,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -31407,7 +31417,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -31417,22 +31427,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>key kelas</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Label = CLASS_CENTROID_MORE atas 5 sampel clustering/kelas (G2-07)</t>
         </is>
       </c>
     </row>
@@ -31444,7 +31449,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -31454,22 +31459,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>quantum_labels[class][IX]</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Urutan observable dikunci §4.3</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IY</t>
+          <t>class</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>quantum_labels[class][IY]</t>
+          <t>key kelas</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Urutan observable dikunci §4.3</t>
+          <t>Label = CLASS_CENTROID_MORE atas 5 sampel clustering/kelas (G2-07)</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IZ</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>quantum_labels[class][IZ]</t>
+          <t>quantum_labels[class][IX]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>XI</t>
+          <t>IY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>quantum_labels[class][XI]</t>
+          <t>quantum_labels[class][IY]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -31592,7 +31592,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>IZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>quantum_labels[class][XX]</t>
+          <t>quantum_labels[class][IZ]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -31629,7 +31629,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>XI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -31644,7 +31644,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>quantum_labels[class][XY]</t>
+          <t>quantum_labels[class][XI]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -31666,7 +31666,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>XZ</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>quantum_labels[class][XZ]</t>
+          <t>quantum_labels[class][XX]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -31703,7 +31703,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YI</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -31718,7 +31718,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>quantum_labels[class][YI]</t>
+          <t>quantum_labels[class][XY]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -31740,7 +31740,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YX</t>
+          <t>XZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -31755,7 +31755,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>quantum_labels[class][YX]</t>
+          <t>quantum_labels[class][XZ]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -31777,7 +31777,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YY</t>
+          <t>YI</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -31792,7 +31792,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>quantum_labels[class][YY]</t>
+          <t>quantum_labels[class][YI]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>YX</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>quantum_labels[class][YZ]</t>
+          <t>quantum_labels[class][YX]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ZI</t>
+          <t>YY</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>quantum_labels[class][ZI]</t>
+          <t>quantum_labels[class][YY]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>quantum_labels[class][ZX]</t>
+          <t>quantum_labels[class][YZ]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ZY</t>
+          <t>ZI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>quantum_labels[class][ZY]</t>
+          <t>quantum_labels[class][ZI]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -31962,7 +31962,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -31977,7 +31977,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>quantum_labels[class][ZZ]</t>
+          <t>quantum_labels[class][ZX]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -31999,7 +31999,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>n_label_samples</t>
+          <t>ZY</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -32009,12 +32009,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>artifacts/quantum_label_diagnostics.json</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>per_class[class].n_samples</t>
+          <t>quantum_labels[class][ZY]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>G2-07; = 5 (sampel clustering/kelas)</t>
+          <t>Urutan observable dikunci §4.3</t>
         </is>
       </c>
     </row>
@@ -32036,7 +32036,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>n_degenerate_samples_excluded</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -32046,12 +32046,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>artifacts/quantum_label_diagnostics.json</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>per_class[class].n_degenerate_samples_excluded</t>
+          <t>quantum_labels[class][ZZ]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>G2-04; dikeluarkan dari median</t>
+          <t>Urutan observable dikunci §4.3</t>
         </is>
       </c>
     </row>
@@ -32073,7 +32073,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>label_prenorm</t>
+          <t>n_label_samples</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>per_class[class].prenorm</t>
+          <t>per_class[class].n_samples</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>G2-07; norm median sebelum normalisasi</t>
+          <t>G2-07; = 5 (sampel clustering/kelas)</t>
         </is>
       </c>
     </row>
@@ -32110,7 +32110,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>label_degenerate</t>
+          <t>n_degenerate_samples_excluded</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -32125,7 +32125,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>per_class[class].degenerate</t>
+          <t>per_class[class].n_degenerate_samples_excluded</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -32135,81 +32135,81 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>G2-04</t>
+          <t>G2-04; dikeluarkan dari median</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>07_Pairwise_Distance</t>
+          <t>06_Quantum_Labels</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>label_prenorm</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>per_class_pair</t>
+          <t>per_class</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/quantum_label_diagnostics.json</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>per_class[class].prenorm</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>G2-07; norm median sebelum normalisasi</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>07_Pairwise_Distance</t>
+          <t>06_Quantum_Labels</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>label_degenerate</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>per_class_pair</t>
+          <t>per_class</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/quantum_label_diagnostics.json</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>per_class[class].degenerate</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>G2-04</t>
         </is>
       </c>
     </row>
@@ -32221,7 +32221,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -32231,17 +32231,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -32253,7 +32258,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -32263,17 +32268,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -32285,7 +32295,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -32300,7 +32310,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -32317,7 +32327,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -32332,7 +32342,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -32349,7 +32359,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>class_i</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -32364,12 +32374,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -32381,7 +32391,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>class_j</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -32396,12 +32406,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -32413,7 +32423,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S_value</t>
+          <t>class_i</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -32423,17 +32433,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>artifacts/correlation_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>S[i][j]</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
@@ -32445,7 +32455,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>cosine_distance</t>
+          <t>class_j</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -32455,12 +32465,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>cosine distance antar label</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -32477,7 +32487,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>simplex_bound</t>
+          <t>S_value</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -32487,22 +32497,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>artifacts/correlation_matrix.npy</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>S[i][j]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>1 + 1/(K-1)</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32519,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>separation_ratio</t>
+          <t>cosine_distance</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -32529,91 +32534,86 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>cosine_distance / simplex_bound</t>
+          <t>cosine distance antar label</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Minimum lintas pasangan = min_separation_ratio (G2-06)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>08_Dimension_Activity</t>
+          <t>07_Pairwise_Distance</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>simplex_bound</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>per_observable</t>
+          <t>per_class_pair</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>1 + 1/(K-1)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>08_Dimension_Activity</t>
+          <t>07_Pairwise_Distance</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>separation_ratio</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>per_observable</t>
+          <t>per_class_pair</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>cosine_distance / simplex_bound</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>Minimum lintas pasangan = min_separation_ratio (G2-06)</t>
         </is>
       </c>
     </row>
@@ -32625,7 +32625,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -32635,17 +32635,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -32657,7 +32662,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -32667,17 +32672,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -32689,7 +32699,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -32704,7 +32714,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -32721,7 +32731,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -32736,7 +32746,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -32753,7 +32763,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>observable</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -32763,22 +32773,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Pseudocode §4.3</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>urutan observable</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>15 observable</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32795,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>is_yodd</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -32800,17 +32805,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Pseudocode §4.3</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>[IY, XY, YI, YX, YZ, ZY]</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -32822,7 +32827,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>mean_abs</t>
+          <t>observable</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -32832,22 +32837,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>Pseudocode §4.3</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>urutan observable</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Definisi statistik aktivitas menunggu G2-05</t>
+          <t>15 observable</t>
         </is>
       </c>
     </row>
@@ -32859,7 +32864,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>max_abs</t>
+          <t>is_yodd</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -32869,22 +32874,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>Pseudocode §4.3</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[IY, XY, YI, YX, YZ, ZY]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Definisi menunggu G2-05</t>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>std_abs</t>
+          <t>mean_abs</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -32921,7 +32921,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Definisi menunggu G2-05</t>
+          <t>Definisi statistik aktivitas menunggu G2-05</t>
         </is>
       </c>
     </row>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>active_threshold</t>
+          <t>max_abs</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -32943,17 +32943,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>active_dim_threshold</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Definisi menunggu G2-05</t>
         </is>
       </c>
     </row>
@@ -32965,7 +32970,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>std_abs</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -32980,17 +32985,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>max_abs &gt; active_threshold</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Konsisten dengan active_dimensions</t>
+          <t>Definisi menunggu G2-05</t>
         </is>
       </c>
     </row>
@@ -33002,7 +33007,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>norm_fraction</t>
+          <t>active_threshold</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -33012,96 +33017,91 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>artifacts/quantum_labels.json</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>active_dim_threshold</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Definisi menunggu G2-05</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>09_Per_Class_Metrics</t>
+          <t>08_Dimension_Activity</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>per_class</t>
+          <t>per_observable</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>max_abs &gt; active_threshold</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>Konsisten dengan active_dimensions</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>09_Per_Class_Metrics</t>
+          <t>08_Dimension_Activity</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>norm_fraction</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>per_class</t>
+          <t>per_observable</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>artifacts/quantum_labels.json</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>Definisi menunggu G2-05</t>
         </is>
       </c>
     </row>
@@ -33113,7 +33113,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -33123,17 +33123,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -33145,7 +33150,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -33155,17 +33160,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33187,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -33192,7 +33202,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -33209,7 +33219,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -33224,7 +33234,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -33241,7 +33251,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -33256,12 +33266,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -33273,7 +33283,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -33283,22 +33293,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>logs/confusion_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Dihitung dari confusion matrix official test</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33315,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>class</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -33320,22 +33325,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>logs/confusion_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Dihitung dari confusion matrix official test</t>
         </is>
       </c>
     </row>
@@ -33347,7 +33347,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -33362,7 +33362,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>support</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -33421,7 +33421,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -33458,7 +33458,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -33490,74 +33490,74 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>10_Confusion_Data</t>
+          <t>09_Per_Class_Metrics</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>per_cm_cell</t>
+          <t>per_class</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/confusion_matrix.npy</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>Dihitung dari confusion matrix official test</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>10_Confusion_Data</t>
+          <t>09_Per_Class_Metrics</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>wrong</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>per_cm_cell</t>
+          <t>per_class</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/confusion_matrix.npy</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>wrong</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>Dihitung dari confusion matrix official test</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -33579,17 +33579,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -33601,7 +33606,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -33611,17 +33616,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -33633,7 +33643,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -33648,7 +33658,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -33665,7 +33675,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -33680,7 +33690,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -33697,7 +33707,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>actual_class</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -33707,17 +33717,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>logs/confusion_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>indeks baris</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -33729,7 +33739,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>predicted_class</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -33739,17 +33749,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>logs/confusion_matrix.npy</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>indeks kolom</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -33761,7 +33771,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>actual_class</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -33776,86 +33786,76 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>cm[i][j]</t>
+          <t>indeks baris</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>11_Test_Predictions</t>
+          <t>10_Confusion_Data</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>predicted_class</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>per_sample</t>
+          <t>per_cm_cell</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/confusion_matrix.npy</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>indeks kolom</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Dijoin lewat run_name dari config.json</t>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>11_Test_Predictions</t>
+          <t>10_Confusion_Data</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>count</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>per_sample</t>
+          <t>per_cm_cell</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>01_Run_Summary (template)</t>
+          <t>logs/confusion_matrix.npy</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>run_uid</t>
+          <t>cm[i][j]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -33877,17 +33877,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Dijoin lewat run_name dari config.json</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33904,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -33909,17 +33914,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>config.json (manifest run)</t>
+          <t>01_Run_Summary (template)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>n_classes</t>
+          <t>run_uid</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>run_uid = condition_id-S&lt;seed&gt;; dijoin lewat run_name</t>
         </is>
       </c>
     </row>
@@ -33931,7 +33941,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -33946,7 +33956,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -33963,7 +33973,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -33978,7 +33988,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>n_classes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -33995,7 +34005,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>sample_id</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -34005,22 +34015,17 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Identitas sampel belum disimpan (G4-02)</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -34032,7 +34037,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>mnist_index</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -34042,22 +34047,17 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>config.json (manifest run)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Indeks MNIST asli belum disimpan per sampel test (G4-02)</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -34069,7 +34069,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>true_class</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -34079,17 +34079,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>artifacts/y_test.npy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>y_test[i]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Identitas sampel belum disimpan (G4-02)</t>
         </is>
       </c>
     </row>
@@ -34101,7 +34106,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>pred_class</t>
+          <t>mnist_index</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -34126,7 +34131,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>FINAL_EVALUATION belum menyimpan prediksi per sampel (G3-02)</t>
+          <t>Indeks MNIST asli belum disimpan per sampel test (G4-02)</t>
         </is>
       </c>
     </row>
@@ -34138,7 +34143,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>distance_true</t>
+          <t>true_class</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -34148,22 +34153,17 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>artifacts/y_test.npy</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>y_test[i]</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>FINAL_EVALUATION belum menyimpan prediksi per sampel (G3-02)</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -34175,7 +34175,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>distance_pred</t>
+          <t>pred_class</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -34212,7 +34212,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>distance_true</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -34249,7 +34249,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>distance_pred</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -34264,81 +34264,91 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>true_class == pred_class</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Bergantung pred_class (GAP)</t>
+          <t>FINAL_EVALUATION belum menyimpan prediksi per sampel (G3-02)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>12_Seed_Aggregation</t>
+          <t>11_Test_Predictions</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>per_condition</t>
+          <t>per_sample</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>FINAL_EVALUATION belum menyimpan prediksi per sampel (G3-02)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12_Seed_Aggregation</t>
+          <t>11_Test_Predictions</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>per_condition</t>
+          <t>per_sample</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>true_class == pred_class</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Bergantung pred_class (GAP)</t>
         </is>
       </c>
     </row>
@@ -34350,7 +34360,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -34365,7 +34375,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -34382,7 +34392,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -34397,7 +34407,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -34414,7 +34424,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -34429,7 +34439,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -34446,7 +34456,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>n_seeds</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -34456,22 +34466,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>01_Run_Summary (5 seed per condition_id)</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>count run COMPLETED</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Agregator G1-04</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -34483,7 +34488,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>accuracy_mean</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -34493,22 +34498,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>01_Run_Summary (5 seed per condition_id)</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Agregator G1-04 (SAP §7)</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>accuracy_sd</t>
+          <t>n_seeds</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -34535,7 +34535,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>count run COMPLETED</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Agregator G1-04 (SAP §7)</t>
+          <t>Agregator G1-04</t>
         </is>
       </c>
     </row>
@@ -34557,7 +34557,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>accuracy_median</t>
+          <t>accuracy_mean</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>accuracy_iqr</t>
+          <t>accuracy_sd</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>f1_mean</t>
+          <t>accuracy_median</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -34646,7 +34646,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>f1_sd</t>
+          <t>accuracy_iqr</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -34683,7 +34683,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>min_sep_mean</t>
+          <t>f1_mean</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -34742,7 +34742,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>min_sep_sd</t>
+          <t>f1_sd</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -34757,7 +34757,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -34779,7 +34779,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>min_sep_ratio_mean</t>
+          <t>min_sep_mean</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -34794,7 +34794,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>min_separation_ratio</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -34816,7 +34816,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>runtime_mean_sec</t>
+          <t>min_sep_sd</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>total_runtime_sec</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -34848,64 +34848,74 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>13_Paired_Comparison</t>
+          <t>12_Seed_Aggregation</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>min_sep_ratio_mean</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>per_pair</t>
+          <t>per_condition</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>01_Run_Summary (5 seed per condition_id)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>min_separation_ratio</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Agregator G1-04 (SAP §7)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>13_Paired_Comparison</t>
+          <t>12_Seed_Aggregation</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>runtime_mean_sec</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>per_pair</t>
+          <t>per_condition</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>01_Run_Summary (5 seed per condition_id)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>total_runtime_sec</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Agregator G1-04 (SAP §7)</t>
         </is>
       </c>
     </row>
@@ -34917,7 +34927,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -34932,7 +34942,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -34949,7 +34959,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -34964,7 +34974,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -34981,7 +34991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>condition_more_hd</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -34996,7 +35006,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>condition_more_hd</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -35013,7 +35023,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>condition_more_hd_c</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -35028,7 +35038,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>condition_more_hd_c</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -35045,7 +35055,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>run_uid_more_hd</t>
+          <t>condition_more_hd</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -35060,7 +35070,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>run_uid_more_hd</t>
+          <t>condition_more_hd</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -35077,7 +35087,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>run_uid_more_hd_c</t>
+          <t>condition_more_hd_c</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -35092,7 +35102,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>run_uid_more_hd_c</t>
+          <t>condition_more_hd_c</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -35109,7 +35119,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>accuracy_more_hd</t>
+          <t>run_uid_more_hd</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -35119,22 +35129,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>01_Run_Summary (pasangan A/D seed sama)</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>run_uid_more_hd</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>SAP §6 estimand primer</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -35146,7 +35151,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>accuracy_more_hd_c</t>
+          <t>run_uid_more_hd_c</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -35156,22 +35161,17 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>01_Run_Summary (pasangan A/D seed sama)</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>run_uid_more_hd_c</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>SAP §6 estimand primer</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -35183,7 +35183,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>delta_accuracy</t>
+          <t>accuracy_more_hd</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -35198,7 +35198,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>D - A</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -35220,7 +35220,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>f1_more_hd</t>
+          <t>accuracy_more_hd_c</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -35235,7 +35235,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>f1_more_hd_c</t>
+          <t>delta_accuracy</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -35272,7 +35272,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>D - A</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>delta_f1</t>
+          <t>f1_more_hd</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -35309,7 +35309,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>D - A</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -35331,7 +35331,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>min_sep_more_hd</t>
+          <t>f1_more_hd_c</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -35368,7 +35368,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>min_sep_more_hd_c</t>
+          <t>delta_f1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -35383,7 +35383,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>min_separation</t>
+          <t>D - A</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>delta_min_sep</t>
+          <t>min_sep_more_hd</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>D - A</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>min_sep_ratio_more_hd</t>
+          <t>min_sep_more_hd_c</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -35457,7 +35457,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>min_separation_ratio</t>
+          <t>min_separation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>min_sep_ratio_more_hd_c</t>
+          <t>delta_min_sep</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>min_separation_ratio</t>
+          <t>D - A</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>delta_min_sep_ratio</t>
+          <t>min_sep_ratio_more_hd</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>D - A</t>
+          <t>min_separation_ratio</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -35548,59 +35548,64 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>14_Dashboard</t>
+          <t>13_Paired_Comparison</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>KPI</t>
+          <t>min_sep_ratio_more_hd_c</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>per_kpi</t>
+          <t>per_pair</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>01_Run_Summary (pasangan A/D seed sama)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>label KPI</t>
+          <t>min_separation_ratio</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>SAP §6 estimand primer</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>14_Dashboard</t>
+          <t>13_Paired_Comparison</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>delta_min_sep_ratio</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>per_kpi</t>
+          <t>per_pair</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>01_Run_Summary</t>
+          <t>01_Run_Summary (pasangan A/D seed sama)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>D - A</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -35610,71 +35615,76 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Planned/Completed/Completion % dihitung dari kolom status 01</t>
+          <t>SAP §6 estimand primer</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>15_Classical_Baselines</t>
+          <t>14_Dashboard</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>per_baseline_row</t>
+          <t>per_kpi</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>label KPI</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>STATIC</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>15_Classical_Baselines</t>
+          <t>14_Dashboard</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>per_baseline_row</t>
+          <t>per_kpi</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>template (prefilled)</t>
+          <t>01_Run_Summary</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>status</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Planned/Completed/Completion % dihitung dari kolom status 01</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35696,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -35701,7 +35711,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -35718,7 +35728,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -35733,7 +35743,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -35750,7 +35760,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -35765,7 +35775,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -35782,7 +35792,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>source_run_uid_A</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -35797,7 +35807,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_run_uid_A</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -35814,7 +35824,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>check_run_uid_D</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -35829,7 +35839,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>check_run_uid_D</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -35846,7 +35856,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>input_hash_match_A_D</t>
+          <t>source_run_uid_A</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -35856,22 +35866,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>baseline_cell_manifest.json</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>input_array_sha256 (A vs D)</t>
+          <t>source_run_uid_A</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>TRUE bila RESOLVE_BASELINE_SOURCE lolos cek hash</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -35883,7 +35888,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>C_selected</t>
+          <t>check_run_uid_D</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -35893,22 +35898,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>runs/baselines/baseline_results.csv</t>
+          <t>template (prefilled)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>C_selected</t>
+          <t>check_run_uid_D</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>n/a untuk NC dan chance</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -35920,7 +35920,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>lr_converged</t>
+          <t>input_hash_match_A_D</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -35930,12 +35930,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LR_cv_log.json</t>
+          <t>baseline_cell_manifest.json</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>grid[C_selected].converged</t>
+          <t>input_array_sha256 (A vs D)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -35945,7 +35945,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>n/a untuk NC dan chance</t>
+          <t>TRUE bila RESOLVE_BASELINE_SOURCE lolos cek hash</t>
         </is>
       </c>
     </row>
@@ -35957,7 +35957,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>C_selected</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -35972,12 +35972,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>C_selected</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>n/a untuk NC dan chance</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35994,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>macro_f1</t>
+          <t>lr_converged</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -35999,17 +36004,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>runs/baselines/baseline_results.csv</t>
+          <t>LR_cv_log.json</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>macro_f1</t>
+          <t>grid[C_selected].converged</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>n/a untuk NC dan chance</t>
         </is>
       </c>
     </row>
@@ -36021,7 +36031,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>chance_1_over_K</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -36031,17 +36041,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>runs/baselines/baseline_results.csv</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1/K</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -36053,7 +36063,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>accuracy_more_hd</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -36063,22 +36073,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>01_Run_Summary</t>
+          <t>runs/baselines/baseline_results.csv</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>Dari run A/D yang ditautkan</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -36090,7 +36095,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>accuracy_more_hd_c</t>
+          <t>chance_1_over_K</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -36100,22 +36105,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>01_Run_Summary</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>1/K</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>Dari run A/D yang ditautkan</t>
         </is>
       </c>
     </row>
@@ -36127,7 +36127,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>delta_acc_more_hd_minus_baseline</t>
+          <t>accuracy_more_hd</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>sheet ini</t>
+          <t>01_Run_Summary</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>kuantum - baseline</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -36152,7 +36152,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Deskriptif (SAP §10.2)</t>
+          <t>Dari run A/D yang ditautkan</t>
         </is>
       </c>
     </row>
@@ -36164,7 +36164,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>delta_acc_more_hd_c_minus_baseline</t>
+          <t>accuracy_more_hd_c</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -36174,12 +36174,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>sheet ini</t>
+          <t>01_Run_Summary</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>kuantum - baseline</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -36189,7 +36189,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Deskriptif (SAP §10.2)</t>
+          <t>Dari run A/D yang ditautkan</t>
         </is>
       </c>
     </row>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>f1_more_hd</t>
+          <t>delta_acc_more_hd_minus_baseline</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -36211,12 +36211,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>01_Run_Summary</t>
+          <t>sheet ini</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>kuantum - baseline</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -36226,7 +36226,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Dari run A/D yang ditautkan</t>
+          <t>Deskriptif (SAP §10.2)</t>
         </is>
       </c>
     </row>
@@ -36238,7 +36238,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>f1_more_hd_c</t>
+          <t>delta_acc_more_hd_c_minus_baseline</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -36248,12 +36248,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>01_Run_Summary</t>
+          <t>sheet ini</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>kuantum - baseline</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -36263,7 +36263,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Dari run A/D yang ditautkan</t>
+          <t>Deskriptif (SAP §10.2)</t>
         </is>
       </c>
     </row>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>delta_f1_more_hd_minus_baseline</t>
+          <t>f1_more_hd</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -36285,12 +36285,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>sheet ini</t>
+          <t>01_Run_Summary</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>kuantum - baseline</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -36300,7 +36300,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Deskriptif (SAP §10.2)</t>
+          <t>Dari run A/D yang ditautkan</t>
         </is>
       </c>
     </row>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>delta_f1_more_hd_c_minus_baseline</t>
+          <t>f1_more_hd_c</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -36322,12 +36322,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>sheet ini</t>
+          <t>01_Run_Summary</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>kuantum - baseline</t>
+          <t>f1_macro</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Deskriptif (SAP §10.2)</t>
+          <t>Dari run A/D yang ditautkan</t>
         </is>
       </c>
     </row>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>delta_f1_more_hd_minus_baseline</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -36359,12 +36359,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>runs/baselines/baseline_results.csv</t>
+          <t>sheet ini</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>keberadaan baris</t>
+          <t>kuantum - baseline</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -36374,81 +36374,81 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>PLANNED/COMPLETED</t>
+          <t>Deskriptif (SAP §10.2)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>16_MORE_Reference</t>
+          <t>15_Classical_Baselines</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>delta_f1_more_hd_c_minus_baseline</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>per_K</t>
+          <t>per_baseline_row</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Wu et al. (2023) Tabel I</t>
+          <t>sheet ini</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>kuantum - baseline</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Nilai literatur, tidak direproduksi</t>
+          <t>Deskriptif (SAP §10.2)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>16_MORE_Reference</t>
+          <t>15_Classical_Baselines</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MORE_task</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>per_K</t>
+          <t>per_baseline_row</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Wu et al. (2023) Tabel I</t>
+          <t>runs/baselines/baseline_results.csv</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>MORE_task</t>
+          <t>keberadaan baris</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Nilai literatur, tidak direproduksi</t>
+          <t>PLANNED/COMPLETED</t>
         </is>
       </c>
     </row>
@@ -36460,7 +36460,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MORE_without_R_accuracy_pct</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -36475,7 +36475,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>MORE_without_R_accuracy_pct</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -36497,7 +36497,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MORE_with_R_accuracy_pct</t>
+          <t>MORE_task</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -36512,7 +36512,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>MORE_with_R_accuracy_pct</t>
+          <t>MORE_task</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>MORE_without_R_accuracy_pct</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -36549,7 +36549,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>MORE_without_R_accuracy_pct</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -36571,7 +36571,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>protocol_note</t>
+          <t>MORE_with_R_accuracy_pct</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>protocol_note</t>
+          <t>MORE_with_R_accuracy_pct</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -36603,69 +36603,74 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>17_JalurB_Selection</t>
+          <t>16_MORE_Reference</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>jalurb_run_name</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>per_jalurb_run</t>
+          <t>per_K</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>config.json Jalur B</t>
+          <t>Wu et al. (2023) Tabel I</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>run_name</t>
+          <t>role</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Nilai literatur, tidak direproduksi</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>17_JalurB_Selection</t>
+          <t>16_MORE_Reference</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>source_run_uid</t>
+          <t>protocol_note</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>per_jalurb_run</t>
+          <t>per_K</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>config.json Jalur B</t>
+          <t>Wu et al. (2023) Tabel I</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>source_run_uid</t>
+          <t>protocol_note</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>STATIC</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Ditambahkan audit 2026-09-27</t>
+          <t>Nilai literatur, tidak direproduksi</t>
         </is>
       </c>
     </row>
@@ -36677,7 +36682,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>condition_id</t>
+          <t>jalurb_run_name</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -36692,17 +36697,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>source_run_uid</t>
+          <t>run_name</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Prefix source_run_uid</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -36714,7 +36714,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>source_run_uid</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -36729,12 +36729,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>source_run_uid</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Ditambahkan audit 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36746,7 +36751,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>condition_id</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -36761,7 +36766,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>source_run_uid</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -36771,7 +36776,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>LENGTH(classes)</t>
+          <t>Prefix source_run_uid</t>
         </is>
       </c>
     </row>
@@ -36783,7 +36788,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -36798,7 +36803,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>feature_method</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -36815,7 +36820,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -36830,12 +36835,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>architecture</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>LENGTH(classes)</t>
         </is>
       </c>
     </row>
@@ -36847,7 +36857,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>selection_method</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -36862,7 +36872,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>selection_method</t>
+          <t>feature_method</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -36879,7 +36889,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>n_eligible_eval_ids</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -36894,17 +36904,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>n_eligible_eval_ids</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Hanya phase == optimization (G1-06)</t>
         </is>
       </c>
     </row>
@@ -36916,7 +36921,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>selected_eval_id</t>
+          <t>selection_method</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -36931,7 +36936,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>selected_eval_id</t>
+          <t>selection_method</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -36948,7 +36953,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>selected_phase</t>
+          <t>n_eligible_eval_ids</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -36958,12 +36963,12 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>source logs/selected_checkpoint.json</t>
+          <t>config.json Jalur B</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>selected_metrics.phase</t>
+          <t>n_eligible_eval_ids</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -36973,7 +36978,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Harus optimization</t>
+          <t>Hanya phase == optimization (G1-06)</t>
         </is>
       </c>
     </row>
@@ -36985,7 +36990,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>selected_pseudo_accuracy_val</t>
+          <t>selected_eval_id</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -36995,12 +37000,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>source logs/selected_checkpoint.json</t>
+          <t>config.json Jalur B</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>selected_metrics.pseudo_accuracy_val</t>
+          <t>selected_eval_id</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -37017,7 +37022,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>selected_min_separation_val</t>
+          <t>selected_phase</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -37032,12 +37037,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>selected_metrics.min_separation_val</t>
+          <t>selected_metrics.phase</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Harus optimization</t>
         </is>
       </c>
     </row>
@@ -37049,7 +37059,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>selected_mean_true_distance_val</t>
+          <t>selected_pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -37064,7 +37074,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>selected_metrics.mean_true_distance_val</t>
+          <t>selected_metrics.pseudo_accuracy_val</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -37081,7 +37091,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>selected_train_loss</t>
+          <t>selected_min_separation_val</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -37096,7 +37106,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>selected_metrics.train_loss</t>
+          <t>selected_metrics.min_separation_val</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -37113,7 +37123,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>max_nfev_supervised</t>
+          <t>selected_mean_true_distance_val</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -37123,22 +37133,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>config.json Jalur B</t>
+          <t>source logs/selected_checkpoint.json</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>max_nfev_supervised</t>
+          <t>selected_metrics.mean_true_distance_val</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>Diwarisi dari run sumber</t>
         </is>
       </c>
     </row>
@@ -37150,7 +37155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>supervised_nfev</t>
+          <t>selected_train_loss</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -37160,12 +37165,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>config.json Jalur B</t>
+          <t>source logs/selected_checkpoint.json</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>supervised_optimizer_result.nfev</t>
+          <t>selected_metrics.train_loss</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -37182,7 +37187,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>supervised_final_point_eval_id</t>
+          <t>max_nfev_supervised</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -37197,12 +37202,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>supervised_optimizer_result.final_point_eval_id</t>
+          <t>max_nfev_supervised</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Diwarisi dari run sumber</t>
         </is>
       </c>
     </row>
@@ -37214,7 +37224,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>supervised_nfev</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -37229,7 +37239,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>final_metrics.accuracy</t>
+          <t>supervised_optimizer_result.nfev</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -37246,7 +37256,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>precision_macro</t>
+          <t>supervised_final_point_eval_id</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -37261,7 +37271,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>final_metrics.precision</t>
+          <t>supervised_optimizer_result.final_point_eval_id</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -37278,7 +37288,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>recall_macro</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -37293,7 +37303,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>final_metrics.recall</t>
+          <t>final_metrics.accuracy</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -37310,7 +37320,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>f1_macro</t>
+          <t>precision_macro</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -37325,7 +37335,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>final_metrics.f1_score</t>
+          <t>final_metrics.precision</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -37342,7 +37352,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>test_used_for_selection</t>
+          <t>recall_macro</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -37357,17 +37367,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>test_used_for_selection</t>
+          <t>final_metrics.recall</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>Harus FALSE</t>
         </is>
       </c>
     </row>
@@ -37379,37 +37384,106 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
+          <t>f1_macro</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>per_jalurb_run</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>config.json Jalur B</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>final_metrics.f1_score</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>17_JalurB_Selection</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>test_used_for_selection</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>per_jalurb_run</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>config.json Jalur B</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>test_used_for_selection</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Harus FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>17_JalurB_Selection</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
           <t>total_runtime_sec</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>per_jalurb_run</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>config.json Jalur B</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E328" t="inlineStr">
         <is>
           <t>total_runtime_sec</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>Ditambahkan audit 2026-09-27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G326"/>
+  <autoFilter ref="A3:G328"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -55268,7 +55342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR243"/>
+  <dimension ref="A1:AT243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -55315,6 +55389,8 @@
     <col width="16" customWidth="1" min="42" max="42"/>
     <col width="16" customWidth="1" min="43" max="43"/>
     <col width="17" customWidth="1" min="44" max="44"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -55545,6 +55621,16 @@
           <t>centroid_source</t>
         </is>
       </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>val_monitor_policy</t>
+        </is>
+      </c>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>n_val_monitor_per_class</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -55677,6 +55763,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -55809,6 +55900,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -55941,6 +56037,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -56073,6 +56174,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -56205,6 +56311,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -56337,6 +56448,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -56469,6 +56585,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -56601,6 +56722,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -56733,6 +56859,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -56865,6 +56996,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -57000,6 +57136,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -57135,6 +57276,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -57270,6 +57416,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -57405,6 +57556,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -57540,6 +57696,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -57675,6 +57836,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -57810,6 +57976,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57945,6 +58116,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58080,6 +58256,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -58215,6 +58396,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -58349,6 +58535,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -58483,6 +58674,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -58617,6 +58813,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -58751,6 +58952,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -58885,6 +59091,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -59019,6 +59230,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -59153,6 +59369,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -59287,6 +59508,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -59421,6 +59647,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -59555,6 +59786,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -59687,6 +59923,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -59819,6 +60060,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -59951,6 +60197,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -60083,6 +60334,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -60215,6 +60471,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -60347,6 +60608,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -60479,6 +60745,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -60611,6 +60882,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -60743,6 +61019,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -60875,6 +61156,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -61010,6 +61296,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -61145,6 +61436,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -61280,6 +61576,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -61415,6 +61716,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -61550,6 +61856,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -61685,6 +61996,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -61820,6 +62136,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -61955,6 +62276,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -62090,6 +62416,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -62225,6 +62556,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -62359,6 +62695,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -62493,6 +62834,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -62627,6 +62973,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -62761,6 +63112,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -62895,6 +63251,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -63029,6 +63390,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -63163,6 +63529,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -63297,6 +63668,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -63431,6 +63807,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -63565,6 +63946,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -63697,6 +64083,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -63829,6 +64220,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -63961,6 +64357,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -64093,6 +64494,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -64225,6 +64631,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -64357,6 +64768,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -64489,6 +64905,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -64621,6 +65042,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -64753,6 +65179,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -64885,6 +65316,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -65020,6 +65456,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -65155,6 +65596,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -65290,6 +65736,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -65425,6 +65876,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -65560,6 +66016,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -65695,6 +66156,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -65830,6 +66296,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -65965,6 +66436,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -66100,6 +66576,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -66235,6 +66716,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -66369,6 +66855,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -66503,6 +66994,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -66637,6 +67133,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -66771,6 +67272,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -66905,6 +67411,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -67039,6 +67550,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -67173,6 +67689,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -67307,6 +67828,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -67441,6 +67967,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -67575,6 +68106,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -67707,6 +68243,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -67839,6 +68380,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -67971,6 +68517,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -68103,6 +68654,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -68235,6 +68791,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -68367,6 +68928,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -68499,6 +69065,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -68631,6 +69202,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -68763,6 +69339,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -68895,6 +69476,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -69030,6 +69616,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -69165,6 +69756,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -69300,6 +69896,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -69435,6 +70036,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -69570,6 +70176,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -69705,6 +70316,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -69840,6 +70456,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -69975,6 +70596,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -70110,6 +70736,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -70245,6 +70876,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -70379,6 +71015,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -70513,6 +71154,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -70647,6 +71293,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -70781,6 +71432,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -70915,6 +71571,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -71049,6 +71710,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -71183,6 +71849,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -71317,6 +71988,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -71451,6 +72127,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -71585,6 +72266,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -71717,6 +72403,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -71849,6 +72540,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -71981,6 +72677,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -72113,6 +72814,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -72245,6 +72951,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -72377,6 +73088,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -72509,6 +73225,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -72641,6 +73362,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -72773,6 +73499,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -72905,6 +73636,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -73040,6 +73776,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -73175,6 +73916,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -73310,6 +74056,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -73445,6 +74196,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -73580,6 +74336,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -73715,6 +74476,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -73850,6 +74616,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -73985,6 +74756,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -74120,6 +74896,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -74255,6 +75036,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -74389,6 +75175,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -74523,6 +75314,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -74657,6 +75453,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -74791,6 +75592,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -74925,6 +75731,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -75059,6 +75870,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -75193,6 +76009,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -75327,6 +76148,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -75461,6 +76287,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -75595,6 +76426,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -75727,6 +76563,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -75859,6 +76700,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -75991,6 +76837,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -76123,6 +76974,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -76255,6 +77111,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -76387,6 +77248,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -76519,6 +77385,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -76651,6 +77522,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -76783,6 +77659,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -76915,6 +77796,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -77050,6 +77936,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -77185,6 +78076,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -77320,6 +78216,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -77455,6 +78356,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -77590,6 +78496,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -77725,6 +78636,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -77860,6 +78776,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -77995,6 +78916,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -78130,6 +79056,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -78265,6 +79196,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -78399,6 +79335,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -78533,6 +79474,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -78667,6 +79613,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -78801,6 +79752,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -78935,6 +79891,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -79069,6 +80030,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -79203,6 +80169,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -79337,6 +80308,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -79471,6 +80447,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -79605,6 +80586,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -79737,6 +80723,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -79869,6 +80860,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -80001,6 +80997,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -80133,6 +81134,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -80265,6 +81271,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -80397,6 +81408,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -80529,6 +81545,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -80661,6 +81682,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -80793,6 +81819,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -80925,6 +81956,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -81060,6 +82096,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -81195,6 +82236,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -81330,6 +82376,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -81465,6 +82516,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -81600,6 +82656,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -81735,6 +82796,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -81870,6 +82936,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -82005,6 +83076,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -82140,6 +83216,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -82275,6 +83356,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -82409,6 +83495,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -82543,6 +83634,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -82677,6 +83773,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -82811,6 +83912,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -82945,6 +84051,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -83079,6 +84190,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -83213,6 +84329,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -83347,6 +84468,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -83481,6 +84607,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -83615,6 +84746,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -83747,6 +84883,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -83879,6 +85020,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -84011,6 +85157,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -84143,6 +85294,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -84275,6 +85431,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -84407,6 +85568,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -84539,6 +85705,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -84671,6 +85842,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -84803,6 +85979,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -84935,6 +86116,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -85070,6 +86256,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -85205,6 +86396,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -85340,6 +86536,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -85475,6 +86676,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -85610,6 +86816,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -85745,6 +86956,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -85880,6 +87096,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -86015,6 +87236,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -86150,6 +87376,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -86285,6 +87516,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -86419,6 +87655,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -86553,6 +87794,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -86687,6 +87933,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -86821,6 +88072,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -86955,6 +88211,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -87089,6 +88350,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -87223,6 +88489,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -87357,6 +88628,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -87491,6 +88767,11 @@
           <t>CLUSTER_SAMPLES</t>
         </is>
       </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -87623,6 +88904,11 @@
       <c r="AR243" t="inlineStr">
         <is>
           <t>CLUSTER_SAMPLES</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>FULL_VAL</t>
         </is>
       </c>
     </row>
